--- a/DXLibProject_Start/Data/CSV/PlayerModelPath.xlsx
+++ b/DXLibProject_Start/Data/CSV/PlayerModelPath.xlsx
@@ -1,25 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{DAF4C233-35CE-4391-9F1A-05E38B06945F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AC9736-ECBB-46E2-B15F-8F8113B20F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295"/>
+    <workbookView xWindow="7035" yWindow="4365" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerModelPath" sheetId="1" r:id="rId1"/>
     <sheet name="status" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -70,9 +78,6 @@
     <t>Damage.mv1</t>
   </si>
   <si>
-    <t>dead</t>
-  </si>
-  <si>
     <t>animPath[1]</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -102,13 +107,17 @@
   </si>
   <si>
     <t>Damage</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Dead.mv1</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -768,9 +777,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -808,7 +817,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -914,7 +923,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1056,14 +1065,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1078,13 +1087,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -1123,7 +1132,7 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1134,13 +1143,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -1148,7 +1157,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1156,7 +1165,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1164,7 +1173,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1172,7 +1181,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1180,7 +1189,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>5</v>
